--- a/5_Judgemental_Nowcasts_Derivations_Analysis/0_Main_Analysis/EDA_Tables/judgemental_derivations_AR2.xlsx
+++ b/5_Judgemental_Nowcasts_Derivations_Analysis/0_Main_Analysis/EDA_Tables/judgemental_derivations_AR2.xlsx
@@ -492,13 +492,13 @@
         <v>0.4352029183766609</v>
       </c>
       <c r="E2">
-        <v>0.5984434428180319</v>
+        <v>0.5278817260644753</v>
       </c>
       <c r="F2">
-        <v>0.2336463611946927</v>
+        <v>0.1630846444411361</v>
       </c>
       <c r="G2">
-        <v>0.2015565571819682</v>
+        <v>0.2721182739355248</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -510,10 +510,10 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>-0.1311507204286465</v>
+        <v>-0.2017124371822031</v>
       </c>
       <c r="L2">
-        <v>-0.163240524441371</v>
+        <v>-0.09267880768781439</v>
       </c>
       <c r="M2">
         <v>0.6352029183766608</v>
@@ -525,10 +525,10 @@
         <v>-0.3647970816233392</v>
       </c>
       <c r="P2">
-        <v>-0.2015565571819682</v>
+        <v>-0.2721182739355248</v>
       </c>
       <c r="Q2">
-        <v>-0.1348109580640418</v>
+        <v>-0.1628049789110708</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -545,13 +545,13 @@
         <v>0.280777696258258</v>
       </c>
       <c r="E3">
-        <v>0.5698310446372115</v>
+        <v>0.8158350159267664</v>
       </c>
       <c r="F3">
-        <v>0.4506087408954694</v>
+        <v>0.6966127121850244</v>
       </c>
       <c r="G3">
-        <v>-0.1698310446372114</v>
+        <v>-0.4158350159267664</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -563,10 +563,10 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>0.3313864371537274</v>
+        <v>0.5773904084432824</v>
       </c>
       <c r="L3">
-        <v>-0.2890533483789535</v>
+        <v>-0.5350573196685084</v>
       </c>
       <c r="M3">
         <v>0.880777696258258</v>
@@ -578,10 +578,10 @@
         <v>0.880777696258258</v>
       </c>
       <c r="P3">
-        <v>0.1698310446372114</v>
+        <v>0.4158350159267664</v>
       </c>
       <c r="Q3">
-        <v>0.1242121226553057</v>
+        <v>0.4064331560616811</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -598,13 +598,13 @@
         <v>-0.01813221787760042</v>
       </c>
       <c r="E4">
-        <v>0.4888361074519135</v>
+        <v>0.4070688708672613</v>
       </c>
       <c r="F4">
-        <v>0.6707038895743132</v>
+        <v>0.5889366529896609</v>
       </c>
       <c r="G4">
-        <v>-0.6888361074519136</v>
+        <v>-0.6070688708672614</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -616,10 +616,10 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>0.8525716716967128</v>
+        <v>0.7708044351120605</v>
       </c>
       <c r="L4">
-        <v>-0.506968325329514</v>
+        <v>-0.4252010887448617</v>
       </c>
       <c r="M4">
         <v>1.1818677821224</v>
@@ -631,10 +631,10 @@
         <v>1.1818677821224</v>
       </c>
       <c r="P4">
-        <v>0.6525716716967127</v>
+        <v>0.5708044351120605</v>
       </c>
       <c r="Q4">
-        <v>0.4495149301649516</v>
+        <v>0.3465176039095035</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -651,13 +651,13 @@
         <v>-0.1707092582566427</v>
       </c>
       <c r="E5">
-        <v>0.4640669336751295</v>
+        <v>0.4060566115363017</v>
       </c>
       <c r="F5">
-        <v>0.1933576754184868</v>
+        <v>0.135347353279659</v>
       </c>
       <c r="G5">
-        <v>-0.3640669336751295</v>
+        <v>-0.3060566115363017</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -666,13 +666,13 @@
         <v>1</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>-0.07735158283815591</v>
+        <v>-0.1353619049769837</v>
       </c>
       <c r="L5">
-        <v>-0.6347761919317723</v>
+        <v>-0.5767658697929444</v>
       </c>
       <c r="M5">
         <v>0.7292907417433573</v>
@@ -681,13 +681,13 @@
         <v>0.7292907417433573</v>
       </c>
       <c r="O5">
-        <v>0.7292907417433573</v>
+        <v>-0.2707092582566427</v>
       </c>
       <c r="P5">
-        <v>0.0226484171618441</v>
+        <v>-0.03536190497698374</v>
       </c>
       <c r="Q5">
-        <v>0.008245539788707762</v>
+        <v>-0.01082274481472432</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -704,13 +704,13 @@
         <v>0.2925127928898435</v>
       </c>
       <c r="E6">
-        <v>0.4589753847598654</v>
+        <v>0.2658412787400625</v>
       </c>
       <c r="F6">
-        <v>1.051488177649709</v>
+        <v>0.8583540716299061</v>
       </c>
       <c r="G6">
-        <v>-0.7589753847598654</v>
+        <v>-0.5658412787400625</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -722,10 +722,10 @@
         <v>1</v>
       </c>
       <c r="K6">
-        <v>1.644000970539552</v>
+        <v>1.45086686451975</v>
       </c>
       <c r="L6">
-        <v>-0.1664625918700219</v>
+        <v>0.02667151414978097</v>
       </c>
       <c r="M6">
         <v>1.592512792889843</v>
@@ -737,10 +737,10 @@
         <v>1.592512792889843</v>
       </c>
       <c r="P6">
-        <v>0.7589753847598655</v>
+        <v>0.5658412787400626</v>
       </c>
       <c r="Q6">
-        <v>1.020063653732889</v>
+        <v>0.6512079782794215</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -757,13 +757,13 @@
         <v>0.1785643430426489</v>
       </c>
       <c r="E7">
-        <v>0.3811469122973433</v>
+        <v>0.1668148420067005</v>
       </c>
       <c r="F7">
-        <v>-0.3402887446599993</v>
+        <v>-0.5546208149506421</v>
       </c>
       <c r="G7">
-        <v>0.5188530877026482</v>
+        <v>0.733185157993291</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
@@ -775,10 +775,10 @@
         <v>1</v>
       </c>
       <c r="K7">
-        <v>-1.061724401617342</v>
+        <v>-1.276056471907985</v>
       </c>
       <c r="L7">
-        <v>-0.2025825692546944</v>
+        <v>0.01174950103594841</v>
       </c>
       <c r="M7">
         <v>-0.7214356569573426</v>
@@ -790,10 +790,10 @@
         <v>0.2785643430426574</v>
       </c>
       <c r="P7">
-        <v>0.1617244016173504</v>
+        <v>0.3760564719079932</v>
       </c>
       <c r="Q7">
-        <v>0.08391120513602537</v>
+        <v>0.2757190237702615</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -810,43 +810,43 @@
         <v>-0.0837572512271369</v>
       </c>
       <c r="E8">
-        <v>0.4852206541758703</v>
+        <v>0.3071481657186778</v>
       </c>
       <c r="F8">
-        <v>0.1014634029487334</v>
+        <v>-0.07660908550845907</v>
       </c>
       <c r="G8">
-        <v>-0.1852206541758703</v>
+        <v>-0.007148165718677824</v>
       </c>
       <c r="H8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>-0.2822938482784035</v>
+        <v>-0.460366336735596</v>
       </c>
       <c r="L8">
-        <v>-0.5689779054030072</v>
+        <v>-0.3909054169458147</v>
       </c>
       <c r="M8">
-        <v>0.6162427487728631</v>
+        <v>-0.3837572512271369</v>
       </c>
       <c r="N8">
         <v>0.6162427487728631</v>
       </c>
       <c r="O8">
-        <v>0.6162427487728631</v>
+        <v>-0.3837572512271369</v>
       </c>
       <c r="P8">
-        <v>0.01770615172159651</v>
+        <v>-0.007148165718677824</v>
       </c>
       <c r="Q8">
-        <v>0.003279545004811317</v>
+        <v>-0.001146325150683331</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -863,13 +863,13 @@
         <v>0.4608782057348194</v>
       </c>
       <c r="E9">
-        <v>0.5129871263628406</v>
+        <v>0.5498874657267171</v>
       </c>
       <c r="F9">
-        <v>0.6738653320976771</v>
+        <v>0.7107656714615536</v>
       </c>
       <c r="G9">
-        <v>-0.2129871263628577</v>
+        <v>-0.2498874657267342</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -881,10 +881,10 @@
         <v>1</v>
       </c>
       <c r="K9">
-        <v>0.8347435378325135</v>
+        <v>0.87164387719639</v>
       </c>
       <c r="L9">
-        <v>-0.05210892062802122</v>
+        <v>-0.08900925999189771</v>
       </c>
       <c r="M9">
         <v>1.160878205734837</v>
@@ -896,10 +896,10 @@
         <v>1.160878205734837</v>
       </c>
       <c r="P9">
-        <v>0.2129871263628577</v>
+        <v>0.2498874657267341</v>
       </c>
       <c r="Q9">
-        <v>0.2416857652817661</v>
+        <v>0.2927791192068466</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -916,43 +916,43 @@
         <v>-0.4996974281391754</v>
       </c>
       <c r="E10">
-        <v>0.3987129603527378</v>
+        <v>0.1736804633958236</v>
       </c>
       <c r="F10">
-        <v>-0.3009844677864404</v>
+        <v>-0.5260169647433546</v>
       </c>
       <c r="G10">
-        <v>-0.198712960352735</v>
+        <v>0.02631953660417918</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
       </c>
       <c r="I10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
-        <v>-1.000681895925619</v>
+        <v>-1.225714392882533</v>
       </c>
       <c r="L10">
-        <v>-0.8984103884919132</v>
+        <v>-0.6733778915349991</v>
       </c>
       <c r="M10">
         <v>-0.6996974281391782</v>
       </c>
       <c r="N10">
+        <v>-0.6996974281391782</v>
+      </c>
+      <c r="O10">
         <v>0.3003025718608218</v>
       </c>
-      <c r="O10">
-        <v>-0.6996974281391782</v>
-      </c>
       <c r="P10">
-        <v>-0.198712960352735</v>
+        <v>0.02631953660417913</v>
       </c>
       <c r="Q10">
-        <v>-0.1591058698402196</v>
+        <v>0.02699632750890513</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -969,16 +969,16 @@
         <v>0.1813625758282837</v>
       </c>
       <c r="E11">
-        <v>0.4704147728506033</v>
+        <v>0.3086271608792364</v>
       </c>
       <c r="F11">
-        <v>0.03177734867888249</v>
+        <v>-0.1300102632924844</v>
       </c>
       <c r="G11">
-        <v>0.1495852271494013</v>
+        <v>0.3113728391207681</v>
       </c>
       <c r="H11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
@@ -987,13 +987,13 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>-0.4068600754928383</v>
+        <v>-0.5686476874642052</v>
       </c>
       <c r="L11">
-        <v>-0.2890521970223195</v>
+        <v>-0.1272645850509527</v>
       </c>
       <c r="M11">
-        <v>0.5613625758282792</v>
+        <v>-0.4386374241717208</v>
       </c>
       <c r="N11">
         <v>-0.4386374241717208</v>
@@ -1002,10 +1002,10 @@
         <v>-0.4386374241717208</v>
       </c>
       <c r="P11">
-        <v>-0.1495852271494013</v>
+        <v>-0.05135231253579936</v>
       </c>
       <c r="Q11">
-        <v>-0.0318825840220107</v>
+        <v>-0.01598971534968886</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1022,13 +1022,13 @@
         <v>0.2013073288242442</v>
       </c>
       <c r="E12">
-        <v>0.45960676335203</v>
+        <v>0.3194721332081325</v>
       </c>
       <c r="F12">
-        <v>0.1909140921762753</v>
+        <v>0.05077946203237782</v>
       </c>
       <c r="G12">
-        <v>0.01039323664796893</v>
+        <v>0.1505278667918664</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -1040,10 +1040,10 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>-0.07777857899947938</v>
+        <v>-0.2179132091433769</v>
       </c>
       <c r="L12">
-        <v>-0.2582994345277858</v>
+        <v>-0.1181648043838883</v>
       </c>
       <c r="M12">
         <v>0.7313073288242453</v>
@@ -1055,10 +1055,10 @@
         <v>-0.2686926711757547</v>
       </c>
       <c r="P12">
-        <v>-0.01039323664796893</v>
+        <v>-0.1505278667918664</v>
       </c>
       <c r="Q12">
-        <v>-0.004076450046861045</v>
+        <v>-0.03794608687405469</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1075,13 +1075,13 @@
         <v>-0.07125936757448281</v>
       </c>
       <c r="E13">
-        <v>0.4866309068941742</v>
+        <v>0.4935538258476527</v>
       </c>
       <c r="F13">
-        <v>0.07537153931968799</v>
+        <v>0.0822944582731665</v>
       </c>
       <c r="G13">
-        <v>-0.1466309068941708</v>
+        <v>-0.1535538258476493</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -1093,10 +1093,10 @@
         <v>1</v>
       </c>
       <c r="K13">
-        <v>-0.3358878282547982</v>
+        <v>-0.3289649093013197</v>
       </c>
       <c r="L13">
-        <v>-0.557890274468657</v>
+        <v>-0.5648131934221355</v>
       </c>
       <c r="M13">
         <v>0.5887406324255138</v>
@@ -1108,10 +1108,10 @@
         <v>0.5887406324255138</v>
       </c>
       <c r="P13">
-        <v>0.004112171745205173</v>
+        <v>0.01103509069868369</v>
       </c>
       <c r="Q13">
-        <v>0.0006029714723040196</v>
+        <v>0.00169448039535869</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1128,43 +1128,43 @@
         <v>0.02307657371240679</v>
       </c>
       <c r="E14">
-        <v>0.4459418294680377</v>
+        <v>0.2854538301566019</v>
       </c>
       <c r="F14">
-        <v>0.01901840318045589</v>
+        <v>-0.1414695961309799</v>
       </c>
       <c r="G14">
-        <v>0.0040581705319509</v>
+        <v>0.1645461698433867</v>
       </c>
       <c r="H14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
       </c>
       <c r="J14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>-0.4079050231071259</v>
+        <v>-0.5683930224185616</v>
       </c>
       <c r="L14">
-        <v>-0.4228652557556309</v>
+        <v>-0.2623772564441951</v>
       </c>
       <c r="M14">
-        <v>0.5730765737124182</v>
+        <v>-0.4269234262875818</v>
       </c>
       <c r="N14">
         <v>-0.4269234262875818</v>
       </c>
       <c r="O14">
-        <v>-0.4269234262875818</v>
+        <v>0.5730765737124182</v>
       </c>
       <c r="P14">
-        <v>-0.0040581705319509</v>
+        <v>0.1183930224185731</v>
       </c>
       <c r="Q14">
-        <v>-0.0001708285947697693</v>
+        <v>0.01948111837515841</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1181,13 +1181,13 @@
         <v>0.0835432859823011</v>
       </c>
       <c r="E15">
-        <v>0.4898183955613777</v>
+        <v>0.4880370991768954</v>
       </c>
       <c r="F15">
-        <v>-0.1266383184563099</v>
+        <v>-0.1284196148407921</v>
       </c>
       <c r="G15">
-        <v>0.2101816044386109</v>
+        <v>0.2119629008230932</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
@@ -1199,10 +1199,10 @@
         <v>1</v>
       </c>
       <c r="K15">
-        <v>-0.7430950324739973</v>
+        <v>-0.7448763288584797</v>
       </c>
       <c r="L15">
-        <v>-0.4062751095790766</v>
+        <v>-0.4044938131945943</v>
       </c>
       <c r="M15">
         <v>-0.6164567140176875</v>
@@ -1214,10 +1214,10 @@
         <v>0.3835432859823125</v>
       </c>
       <c r="P15">
-        <v>0.04309503247400875</v>
+        <v>0.04487632885849102</v>
       </c>
       <c r="Q15">
-        <v>0.009057783068721202</v>
+        <v>0.00951211684313685</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -1234,43 +1234,43 @@
         <v>-0.05696692470090148</v>
       </c>
       <c r="E16">
-        <v>0.5308500955697427</v>
+        <v>0.5892375486112547</v>
       </c>
       <c r="F16">
-        <v>-0.07611682913117013</v>
+        <v>-0.01772937608965819</v>
       </c>
       <c r="G16">
-        <v>0.01914990443026865</v>
+        <v>-0.03923754861124329</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
       </c>
       <c r="I16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>-0.683083753832083</v>
+        <v>-0.624696300790571</v>
       </c>
       <c r="L16">
-        <v>-0.5878170202706442</v>
+        <v>-0.6462044733121561</v>
       </c>
       <c r="M16">
         <v>-0.6069669247009128</v>
       </c>
       <c r="N16">
+        <v>0.3930330752990872</v>
+      </c>
+      <c r="O16">
         <v>-0.6069669247009128</v>
       </c>
-      <c r="O16">
-        <v>0.3930330752990872</v>
-      </c>
       <c r="P16">
-        <v>0.01914990443026865</v>
+        <v>-0.03923754861124329</v>
       </c>
       <c r="Q16">
-        <v>0.00254854116710557</v>
+        <v>-0.002930899733349635</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -1287,13 +1287,13 @@
         <v>0.4027192445571373</v>
       </c>
       <c r="E17">
-        <v>0.5146509551248899</v>
+        <v>0.498268675818354</v>
       </c>
       <c r="F17">
-        <v>0.2173701996820385</v>
+        <v>0.2009879203755026</v>
       </c>
       <c r="G17">
-        <v>0.1853490448750987</v>
+        <v>0.2017313241816346</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1305,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>-0.07991055576081285</v>
+        <v>-0.09629283506734876</v>
       </c>
       <c r="L17">
-        <v>-0.1119317105677526</v>
+        <v>-0.09554943126121673</v>
       </c>
       <c r="M17">
         <v>0.7027192445571486</v>
@@ -1320,10 +1320,10 @@
         <v>-0.2972807554428514</v>
       </c>
       <c r="P17">
-        <v>-0.1853490448750987</v>
+        <v>-0.2017313241816346</v>
       </c>
       <c r="Q17">
-        <v>-0.114932986226862</v>
+        <v>-0.1217866457998019</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1340,16 +1340,16 @@
         <v>-0.1515848892748725</v>
       </c>
       <c r="E18">
-        <v>0.4741444152223665</v>
+        <v>0.3409278159840826</v>
       </c>
       <c r="F18">
-        <v>0.02255952594751109</v>
+        <v>-0.1106570732907728</v>
       </c>
       <c r="G18">
-        <v>-0.1741444152223836</v>
+        <v>-0.04092781598409972</v>
       </c>
       <c r="H18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="b">
         <v>1</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>-0.4290253633273443</v>
+        <v>-0.5622419625656282</v>
       </c>
       <c r="L18">
-        <v>-0.625729304497239</v>
+        <v>-0.4925127052589551</v>
       </c>
       <c r="M18">
-        <v>0.5484151107251446</v>
+        <v>-0.4515848892748554</v>
       </c>
       <c r="N18">
         <v>0.5484151107251446</v>
@@ -1373,10 +1373,10 @@
         <v>-0.4515848892748554</v>
       </c>
       <c r="P18">
-        <v>-0.1290253633273614</v>
+        <v>-0.04092781598409972</v>
       </c>
       <c r="Q18">
-        <v>-0.02246904644549893</v>
+        <v>-0.0107329907871959</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -1393,13 +1393,13 @@
         <v>0.6988415319442993</v>
       </c>
       <c r="E19">
-        <v>0.4777870639207178</v>
+        <v>0.3924672903298065</v>
       </c>
       <c r="F19">
-        <v>0.6766285958650455</v>
+        <v>0.5913088222741343</v>
       </c>
       <c r="G19">
-        <v>0.02221293607925379</v>
+        <v>0.1075327096701651</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -1411,10 +1411,10 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0.8754701278093733</v>
+        <v>0.790150354218462</v>
       </c>
       <c r="L19">
-        <v>0.2210544680235816</v>
+        <v>0.3063742416144929</v>
       </c>
       <c r="M19">
         <v>1.198841531944328</v>
@@ -1426,10 +1426,10 @@
         <v>0.1988415319443278</v>
       </c>
       <c r="P19">
-        <v>-0.02221293607925379</v>
+        <v>-0.107532709670165</v>
       </c>
       <c r="Q19">
-        <v>-0.03055323002795202</v>
+        <v>-0.1387333634710314</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -1446,43 +1446,43 @@
         <v>0.1826764833261187</v>
       </c>
       <c r="E20">
-        <v>0.4138185309876257</v>
+        <v>0.1122805722851697</v>
       </c>
       <c r="F20">
-        <v>0.3964950143137443</v>
+        <v>0.09495705561128835</v>
       </c>
       <c r="G20">
-        <v>-0.2138185309876257</v>
+        <v>0.08771942771483031</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>0.379171497639863</v>
+        <v>0.077633538937407</v>
       </c>
       <c r="L20">
-        <v>-0.2311420476615071</v>
+        <v>0.07039591104094896</v>
       </c>
       <c r="M20">
         <v>0.9826764833261187</v>
       </c>
       <c r="N20">
-        <v>0.9826764833261187</v>
+        <v>-0.01732351667388135</v>
       </c>
       <c r="O20">
-        <v>0.9826764833261187</v>
+        <v>-0.01732351667388135</v>
       </c>
       <c r="P20">
-        <v>0.2138185309876257</v>
+        <v>-0.08771942771483031</v>
       </c>
       <c r="Q20">
-        <v>0.1238375988152586</v>
+        <v>-0.0243538551500324</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -1499,13 +1499,13 @@
         <v>-0.3243526457088434</v>
       </c>
       <c r="E21">
-        <v>0.3953020579267524</v>
+        <v>0.1844683999603099</v>
       </c>
       <c r="F21">
-        <v>-0.0290505877820853</v>
+        <v>-0.2398842457485278</v>
       </c>
       <c r="G21">
-        <v>-0.2953020579267581</v>
+        <v>-0.08446839996031558</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
@@ -1517,10 +1517,10 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>-0.453403233490923</v>
+        <v>-0.6642368914573655</v>
       </c>
       <c r="L21">
-        <v>-0.7196547036355958</v>
+        <v>-0.5088210456691533</v>
       </c>
       <c r="M21">
         <v>-0.4243526457088377</v>
@@ -1532,10 +1532,10 @@
         <v>-0.4243526457088377</v>
       </c>
       <c r="P21">
-        <v>-0.2953020579267581</v>
+        <v>-0.08446839996031558</v>
       </c>
       <c r="Q21">
-        <v>-0.1043607021278418</v>
+        <v>-0.04766018741998639</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -1552,13 +1552,13 @@
         <v>-0.02531042853141789</v>
       </c>
       <c r="E22">
-        <v>0.4494494662203161</v>
+        <v>0.3627307324263691</v>
       </c>
       <c r="F22">
-        <v>0.5241390376888982</v>
+        <v>0.4374203038949512</v>
       </c>
       <c r="G22">
-        <v>-0.5494494662203161</v>
+        <v>-0.4627307324263691</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -1570,10 +1570,10 @@
         <v>1</v>
       </c>
       <c r="K22">
-        <v>0.5988286091574804</v>
+        <v>0.5121098753635334</v>
       </c>
       <c r="L22">
-        <v>-0.474759894751734</v>
+        <v>-0.388041160957787</v>
       </c>
       <c r="M22">
         <v>1.074689571468582</v>
@@ -1585,10 +1585,10 @@
         <v>1.074689571468582</v>
       </c>
       <c r="P22">
-        <v>0.4988286091574803</v>
+        <v>0.4121098753635333</v>
       </c>
       <c r="Q22">
-        <v>0.2740811130370003</v>
+        <v>0.1906959044671075</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -1605,13 +1605,13 @@
         <v>-0.1841593416869248</v>
       </c>
       <c r="E23">
-        <v>0.429419799243115</v>
+        <v>0.1794263626245832</v>
       </c>
       <c r="F23">
-        <v>0.3452604575561846</v>
+        <v>0.09526702093765275</v>
       </c>
       <c r="G23">
-        <v>-0.5294197992431093</v>
+        <v>-0.2794263626245775</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -1620,13 +1620,13 @@
         <v>1</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>0.2611011158692541</v>
+        <v>0.01110767925072231</v>
       </c>
       <c r="L23">
-        <v>-0.6135791409300397</v>
+        <v>-0.363585704311508</v>
       </c>
       <c r="M23">
         <v>0.9158406583130696</v>
@@ -1635,13 +1635,13 @@
         <v>0.9158406583130696</v>
       </c>
       <c r="O23">
-        <v>0.9158406583130696</v>
+        <v>-0.08415934168693044</v>
       </c>
       <c r="P23">
-        <v>0.1611011158692598</v>
+        <v>-0.08889232074927202</v>
       </c>
       <c r="Q23">
-        <v>0.0852901204213444</v>
+        <v>-0.02483885785222634</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -1658,13 +1658,13 @@
         <v>0.05200447928335454</v>
       </c>
       <c r="E24">
-        <v>0.3825808826190411</v>
+        <v>0.1814061084957765</v>
       </c>
       <c r="F24">
-        <v>0.3545853619023547</v>
+        <v>0.1534105877790901</v>
       </c>
       <c r="G24">
-        <v>-0.3025808826190002</v>
+        <v>-0.1014061084957356</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -1676,10 +1676,10 @@
         <v>1</v>
       </c>
       <c r="K24">
-        <v>0.3265898411856684</v>
+        <v>0.1254150670624037</v>
       </c>
       <c r="L24">
-        <v>-0.3305764033356866</v>
+        <v>-0.129401629212422</v>
       </c>
       <c r="M24">
         <v>0.9720044792833136</v>
@@ -1691,10 +1691,10 @@
         <v>0.9720044792833136</v>
       </c>
       <c r="P24">
-        <v>0.3025808826190002</v>
+        <v>0.1014061084957356</v>
       </c>
       <c r="Q24">
-        <v>0.123026313009891</v>
+        <v>0.02083034257719306</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -1711,13 +1711,13 @@
         <v>2.3218073188947</v>
       </c>
       <c r="E25">
-        <v>0.4158212270970915</v>
+        <v>0.1900831754885381</v>
       </c>
       <c r="F25">
-        <v>2.637628545991797</v>
+        <v>2.411890494383244</v>
       </c>
       <c r="G25">
-        <v>-0.3158212270970972</v>
+        <v>-0.09008317548854378</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -1729,10 +1729,10 @@
         <v>1</v>
       </c>
       <c r="K25">
-        <v>4.859435864886503</v>
+        <v>4.63369781327795</v>
       </c>
       <c r="L25">
-        <v>1.905986091797609</v>
+        <v>2.131724143406162</v>
       </c>
       <c r="M25">
         <v>3.221807318894706</v>
@@ -1744,10 +1744,10 @@
         <v>3.221807318894706</v>
       </c>
       <c r="P25">
-        <v>0.3158212270970973</v>
+        <v>0.09008317548854361</v>
       </c>
       <c r="Q25">
-        <v>1.566295120557808</v>
+        <v>0.4264265308232522</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -1764,13 +1764,13 @@
         <v>-2.209042350248001</v>
       </c>
       <c r="E26">
-        <v>0.1862656172266596</v>
+        <v>-0.6845717329199352</v>
       </c>
       <c r="F26">
-        <v>9.877223266978659</v>
+        <v>9.006385916832064</v>
       </c>
       <c r="G26">
-        <v>-12.08626561722666</v>
+        <v>-11.21542826708007</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -1782,10 +1782,10 @@
         <v>1</v>
       </c>
       <c r="K26">
-        <v>19.56818091673066</v>
+        <v>18.69734356658406</v>
       </c>
       <c r="L26">
-        <v>-2.395307967474661</v>
+        <v>-1.524470617328067</v>
       </c>
       <c r="M26">
         <v>10.690957649752</v>
@@ -1797,10 +1797,10 @@
         <v>10.690957649752</v>
       </c>
       <c r="P26">
-        <v>7.668180916730657</v>
+        <v>6.797343566584063</v>
       </c>
       <c r="Q26">
-        <v>92.67967136055535</v>
+        <v>76.23511917772173</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -1817,13 +1817,13 @@
         <v>-1.840304150385469</v>
       </c>
       <c r="E27">
-        <v>-1.982134026001563</v>
+        <v>-7.463655357282573</v>
       </c>
       <c r="F27">
-        <v>-10.46243817638703</v>
+        <v>-15.94395950766804</v>
       </c>
       <c r="G27">
-        <v>8.622134026001564</v>
+        <v>14.10365535728257</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
@@ -1835,10 +1835,10 @@
         <v>1</v>
       </c>
       <c r="K27">
-        <v>-18.9427423267725</v>
+        <v>-24.42426365805351</v>
       </c>
       <c r="L27">
-        <v>0.1418298756160947</v>
+        <v>5.623351206897103</v>
       </c>
       <c r="M27">
         <v>-8.48030415038547</v>
@@ -1850,10 +1850,10 @@
         <v>-7.48030415038547</v>
       </c>
       <c r="P27">
-        <v>8.622134026001563</v>
+        <v>14.10365535728257</v>
       </c>
       <c r="Q27">
-        <v>106.0758932287948</v>
+        <v>250.8231254162322</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -1870,13 +1870,13 @@
         <v>-0.7406326034063262</v>
       </c>
       <c r="E28">
-        <v>-1.488840052368066</v>
+        <v>-4.144592182330832</v>
       </c>
       <c r="F28">
-        <v>-1.829472655774387</v>
+        <v>-4.485224785737152</v>
       </c>
       <c r="G28">
-        <v>1.08884005236806</v>
+        <v>3.744592182330826</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
@@ -1888,10 +1888,10 @@
         <v>1</v>
       </c>
       <c r="K28">
-        <v>-2.170105259180707</v>
+        <v>-4.825857389143473</v>
       </c>
       <c r="L28">
-        <v>0.7482074489617399</v>
+        <v>3.403959578924505</v>
       </c>
       <c r="M28">
         <v>-0.3406326034063205</v>
@@ -1903,10 +1903,10 @@
         <v>0.6593673965936795</v>
       </c>
       <c r="P28">
-        <v>1.08884005236806</v>
+        <v>3.744592182330826</v>
       </c>
       <c r="Q28">
-        <v>2.798433544997755</v>
+        <v>19.56870472536245</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -1923,43 +1923,43 @@
         <v>1.097457868393073</v>
       </c>
       <c r="E29">
-        <v>0.4888170872567604</v>
+        <v>-0.8877061776737167</v>
       </c>
       <c r="F29">
-        <v>2.295754955649832</v>
+        <v>0.9192316907193552</v>
       </c>
       <c r="G29">
-        <v>-1.19829708725676</v>
+        <v>0.1782261776737175</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>4.102692824042904</v>
+        <v>2.726169559112427</v>
       </c>
       <c r="L29">
-        <v>0.6086407811363124</v>
+        <v>1.985164046066789</v>
       </c>
       <c r="M29">
         <v>2.806937868393072</v>
       </c>
       <c r="N29">
-        <v>2.806937868393072</v>
+        <v>1.806937868393072</v>
       </c>
       <c r="O29">
-        <v>2.806937868393072</v>
+        <v>1.806937868393072</v>
       </c>
       <c r="P29">
-        <v>1.19829708725676</v>
+        <v>-0.1782261776737175</v>
       </c>
       <c r="Q29">
-        <v>4.066077043492896</v>
+        <v>-0.3594268716751026</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -1976,13 +1976,13 @@
         <v>-0.323092118130242</v>
       </c>
       <c r="E30">
-        <v>0.731431855473491</v>
+        <v>0.892999978012982</v>
       </c>
       <c r="F30">
-        <v>-0.901660262656767</v>
+        <v>-0.740092140117276</v>
       </c>
       <c r="G30">
-        <v>0.5785681445265251</v>
+        <v>0.417000021987034</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
@@ -1994,10 +1994,10 @@
         <v>1</v>
       </c>
       <c r="K30">
-        <v>-2.534752380787025</v>
+        <v>-2.373184258247534</v>
       </c>
       <c r="L30">
-        <v>-1.054523973603733</v>
+        <v>-1.216092096143224</v>
       </c>
       <c r="M30">
         <v>-1.633092118130258</v>
@@ -2009,10 +2009,10 @@
         <v>-0.633092118130258</v>
       </c>
       <c r="P30">
-        <v>0.5785681445265251</v>
+        <v>0.417000021987034</v>
       </c>
       <c r="Q30">
-        <v>0.708602712456384</v>
+        <v>0.4433478590654834</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2029,13 +2029,13 @@
         <v>-0.174266296544449</v>
       </c>
       <c r="E31">
-        <v>0.4393764117943757</v>
+        <v>0.464029186385135</v>
       </c>
       <c r="F31">
-        <v>-1.254889884750083</v>
+        <v>-1.230237110159324</v>
       </c>
       <c r="G31">
-        <v>1.080623588205634</v>
+        <v>1.055970813614875</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="K31">
-        <v>-2.949156181294542</v>
+        <v>-2.924503406703783</v>
       </c>
       <c r="L31">
-        <v>-0.6136427083388247</v>
+        <v>-0.6382954829295842</v>
       </c>
       <c r="M31">
         <v>-1.694266296544459</v>
@@ -2062,10 +2062,10 @@
         <v>-0.694266296544459</v>
       </c>
       <c r="P31">
-        <v>1.080623588205634</v>
+        <v>1.055970813614875</v>
       </c>
       <c r="Q31">
-        <v>1.544379880736759</v>
+        <v>1.483114605101847</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -2082,43 +2082,43 @@
         <v>-0.1928103593881966</v>
       </c>
       <c r="E32">
-        <v>0.1639891127141883</v>
+        <v>-0.6356350162097709</v>
       </c>
       <c r="F32">
-        <v>0.5111787533259837</v>
+        <v>-0.2884453755979755</v>
       </c>
       <c r="G32">
-        <v>-0.7039891127141804</v>
+        <v>0.09563501620977888</v>
       </c>
       <c r="H32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32">
-        <v>0.8583683939377791</v>
+        <v>0.05874426501381991</v>
       </c>
       <c r="L32">
-        <v>-0.356799472102385</v>
+        <v>0.4428246568215743</v>
       </c>
       <c r="M32">
-        <v>1.347189640611795</v>
+        <v>0.3471896406117954</v>
       </c>
       <c r="N32">
-        <v>1.347189640611795</v>
+        <v>0.3471896406117954</v>
       </c>
       <c r="O32">
         <v>1.347189640611795</v>
       </c>
       <c r="P32">
-        <v>0.3183683939377871</v>
+        <v>0.09563501620977888</v>
       </c>
       <c r="Q32">
-        <v>0.2241278831645014</v>
+        <v>0.04602490001645162</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -2135,43 +2135,43 @@
         <v>0.2298806514884979</v>
       </c>
       <c r="E33">
-        <v>0.497856732295311</v>
+        <v>0.3241408423207837</v>
       </c>
       <c r="F33">
-        <v>0.2624518358734654</v>
+        <v>0.08873594589893813</v>
       </c>
       <c r="G33">
-        <v>-0.03257118438496753</v>
+        <v>0.1411447055895598</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>0.02704693945161984</v>
+        <v>-0.1466689505229075</v>
       </c>
       <c r="L33">
-        <v>-0.2679760808068131</v>
+        <v>-0.09426019083228582</v>
       </c>
       <c r="M33">
         <v>0.7645951035781544</v>
       </c>
       <c r="N33">
-        <v>0.7645951035781544</v>
+        <v>-0.2354048964218456</v>
       </c>
       <c r="O33">
-        <v>0.7645951035781544</v>
+        <v>-0.2354048964218456</v>
       </c>
       <c r="P33">
-        <v>0.03257118438496753</v>
+        <v>-0.1411447055895598</v>
       </c>
       <c r="Q33">
-        <v>0.01603585222457622</v>
+        <v>-0.04497104583419696</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -2188,13 +2188,13 @@
         <v>0.2402701443875122</v>
       </c>
       <c r="E34">
-        <v>0.5496377906332163</v>
+        <v>0.6660072552246967</v>
       </c>
       <c r="F34">
-        <v>0.4099079350207285</v>
+        <v>0.526277399612209</v>
       </c>
       <c r="G34">
-        <v>-0.1696377906332163</v>
+        <v>-0.2860072552246967</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -2206,10 +2206,10 @@
         <v>1</v>
       </c>
       <c r="K34">
-        <v>0.2701780794082407</v>
+        <v>0.3865475439997212</v>
       </c>
       <c r="L34">
-        <v>-0.3093676462457041</v>
+        <v>-0.4257371108371845</v>
       </c>
       <c r="M34">
         <v>0.8602701443875123</v>
@@ -2221,10 +2221,10 @@
         <v>0.8602701443875123</v>
       </c>
       <c r="P34">
-        <v>0.1696377906332163</v>
+        <v>0.2860072552246968</v>
       </c>
       <c r="Q34">
-        <v>0.1102947729089618</v>
+        <v>0.2192381590585927</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -2241,16 +2241,16 @@
         <v>-0.3601488926112106</v>
       </c>
       <c r="E35">
-        <v>0.4929156585266765</v>
+        <v>0.3437767272872988</v>
       </c>
       <c r="F35">
-        <v>0.0927667659154659</v>
+        <v>-0.05637216532391182</v>
       </c>
       <c r="G35">
-        <v>-0.4529156585266765</v>
+        <v>-0.3037767272872988</v>
       </c>
       <c r="H35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="b">
         <v>1</v>
@@ -2259,13 +2259,13 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>-0.3073821266957447</v>
+        <v>-0.4565210579351224</v>
       </c>
       <c r="L35">
-        <v>-0.8530645511378872</v>
+        <v>-0.7039256198985094</v>
       </c>
       <c r="M35">
-        <v>0.5998511073887893</v>
+        <v>-0.4001488926112106</v>
       </c>
       <c r="N35">
         <v>0.5998511073887893</v>
@@ -2274,10 +2274,10 @@
         <v>-0.4001488926112106</v>
       </c>
       <c r="P35">
-        <v>-0.2673821266957447</v>
+        <v>-0.3037767272872988</v>
       </c>
       <c r="Q35">
-        <v>-0.1211015519906665</v>
+        <v>-0.1265294038257749</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -2294,13 +2294,13 @@
         <v>0.1453061035472806</v>
       </c>
       <c r="E36">
-        <v>0.4910150553647586</v>
+        <v>0.4120709423816584</v>
       </c>
       <c r="F36">
-        <v>0.9263211589120393</v>
+        <v>0.847377045928939</v>
       </c>
       <c r="G36">
-        <v>-0.7810150553647586</v>
+        <v>-0.7020709423816585</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -2312,10 +2312,10 @@
         <v>1</v>
       </c>
       <c r="K36">
-        <v>1.36162726245932</v>
+        <v>1.28268314947622</v>
       </c>
       <c r="L36">
-        <v>-0.345708951817478</v>
+        <v>-0.2667648388343778</v>
       </c>
       <c r="M36">
         <v>1.435306103547281</v>
@@ -2327,10 +2327,10 @@
         <v>1.435306103547281</v>
       </c>
       <c r="P36">
-        <v>0.7810150553647586</v>
+        <v>0.7020709423816585</v>
       </c>
       <c r="Q36">
-        <v>0.8369570257200505</v>
+        <v>0.6969339942391621</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -2347,13 +2347,13 @@
         <v>0.1273487862293673</v>
       </c>
       <c r="E37">
-        <v>0.5994482967366578</v>
+        <v>0.6519408127754134</v>
       </c>
       <c r="F37">
-        <v>0.9346750403813169</v>
+        <v>0.9871675564200725</v>
       </c>
       <c r="G37">
-        <v>-0.8073262541519496</v>
+        <v>-0.8598187701907052</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -2365,10 +2365,10 @@
         <v>1</v>
       </c>
       <c r="K37">
-        <v>1.269901784025976</v>
+        <v>1.322394300064732</v>
       </c>
       <c r="L37">
-        <v>-0.4720995105072905</v>
+        <v>-0.5245920265460461</v>
       </c>
       <c r="M37">
         <v>1.335226743644659</v>
@@ -2380,10 +2380,10 @@
         <v>1.335226743644659</v>
       </c>
       <c r="P37">
-        <v>0.8073262541519496</v>
+        <v>0.8598187701907052</v>
       </c>
       <c r="Q37">
-        <v>0.8573997177577233</v>
+        <v>0.9582820710942839</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -2400,13 +2400,13 @@
         <v>0.1020880707435432</v>
       </c>
       <c r="E38">
-        <v>0.6333318196243403</v>
+        <v>0.8814549586592991</v>
       </c>
       <c r="F38">
-        <v>0.6147720571893032</v>
+        <v>0.862895196224262</v>
       </c>
       <c r="G38">
-        <v>-0.51268398644576</v>
+        <v>-0.7608071254807188</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -2418,10 +2418,10 @@
         <v>1</v>
       </c>
       <c r="K38">
-        <v>0.5962122947542661</v>
+        <v>0.8443354337892249</v>
       </c>
       <c r="L38">
-        <v>-0.5312437488807971</v>
+        <v>-0.7793668879157559</v>
       </c>
       <c r="M38">
         <v>0.9814402375649629</v>
@@ -2433,10 +2433,10 @@
         <v>0.9814402375649629</v>
       </c>
       <c r="P38">
-        <v>0.51268398644576</v>
+        <v>0.7608071254807188</v>
       </c>
       <c r="Q38">
-        <v>0.3675227081126292</v>
+        <v>0.7341661454787689</v>
       </c>
     </row>
     <row r="39" spans="1:17">
@@ -2453,13 +2453,13 @@
         <v>-0.0503823720025918</v>
       </c>
       <c r="E39">
-        <v>0.5452363198887364</v>
+        <v>0.5350086232236873</v>
       </c>
       <c r="F39">
-        <v>0.6748539478861446</v>
+        <v>0.6646262512210954</v>
       </c>
       <c r="G39">
-        <v>-0.7252363198887364</v>
+        <v>-0.7150086232236872</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -2471,10 +2471,10 @@
         <v>1</v>
       </c>
       <c r="K39">
-        <v>0.8044715758835528</v>
+        <v>0.7942438792185036</v>
       </c>
       <c r="L39">
-        <v>-0.5956186918913282</v>
+        <v>-0.585390995226279</v>
       </c>
       <c r="M39">
         <v>1.129617627997408</v>
@@ -2486,10 +2486,10 @@
         <v>1.129617627997408</v>
       </c>
       <c r="P39">
-        <v>0.6244715758835528</v>
+        <v>0.6142438792185037</v>
       </c>
       <c r="Q39">
-        <v>0.4528894675689076</v>
+        <v>0.4391896704035991</v>
       </c>
     </row>
     <row r="40" spans="1:17">
@@ -2506,13 +2506,13 @@
         <v>0.3310636170015632</v>
       </c>
       <c r="E40">
-        <v>0.5509988879663087</v>
+        <v>0.5007400141027678</v>
       </c>
       <c r="F40">
-        <v>0.8380625049678718</v>
+        <v>0.787803631104331</v>
       </c>
       <c r="G40">
-        <v>-0.5069988879663087</v>
+        <v>-0.4567400141027678</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -2524,10 +2524,10 @@
         <v>1</v>
       </c>
       <c r="K40">
-        <v>1.125126121969435</v>
+        <v>1.074867248105894</v>
       </c>
       <c r="L40">
-        <v>-0.2199352709647455</v>
+        <v>-0.1696763971012046</v>
       </c>
       <c r="M40">
         <v>1.287063617001563</v>
@@ -2539,10 +2539,10 @@
         <v>1.287063617001563</v>
       </c>
       <c r="P40">
-        <v>0.5069988879663087</v>
+        <v>0.4567400141027679</v>
       </c>
       <c r="Q40">
-        <v>0.5927456437308665</v>
+        <v>0.5110314426790112</v>
       </c>
     </row>
     <row r="41" spans="1:17">
@@ -2559,13 +2559,13 @@
         <v>-0.2961058799880114</v>
       </c>
       <c r="E41">
-        <v>0.5767737563214386</v>
+        <v>0.6148977852456914</v>
       </c>
       <c r="F41">
-        <v>0.363177916796931</v>
+        <v>0.4013019457211838</v>
       </c>
       <c r="G41">
-        <v>-0.6592837967849423</v>
+        <v>-0.6974078257091951</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -2577,10 +2577,10 @@
         <v>1</v>
       </c>
       <c r="K41">
-        <v>0.1495820772724233</v>
+        <v>0.1877061061966762</v>
       </c>
       <c r="L41">
-        <v>-0.87287963630945</v>
+        <v>-0.9110036652337028</v>
       </c>
       <c r="M41">
         <v>0.7864041604754923</v>
@@ -2592,10 +2592,10 @@
         <v>0.7864041604754923</v>
       </c>
       <c r="P41">
-        <v>0.0670720368089196</v>
+        <v>0.1051960657331724</v>
       </c>
       <c r="Q41">
-        <v>0.04421950708548393</v>
+        <v>0.07336455947613334</v>
       </c>
     </row>
     <row r="42" spans="1:17">
@@ -2612,13 +2612,13 @@
         <v>0.3250145629684917</v>
       </c>
       <c r="E42">
-        <v>0.5308012840444406</v>
+        <v>0.5461074682008229</v>
       </c>
       <c r="F42">
-        <v>0.5975633250554021</v>
+        <v>0.6128695092117844</v>
       </c>
       <c r="G42">
-        <v>-0.2725487620869104</v>
+        <v>-0.2878549462432927</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -2630,10 +2630,10 @@
         <v>1</v>
       </c>
       <c r="K42">
-        <v>0.6643253660663636</v>
+        <v>0.6796315502227459</v>
       </c>
       <c r="L42">
-        <v>-0.2057867210759489</v>
+        <v>-0.2210929052323312</v>
       </c>
       <c r="M42">
         <v>1.066762041010962</v>
@@ -2645,10 +2645,10 @@
         <v>1.066762041010962</v>
       </c>
       <c r="P42">
-        <v>0.2725487620869104</v>
+        <v>0.2878549462432927</v>
       </c>
       <c r="Q42">
-        <v>0.2514474613096684</v>
+        <v>0.2699745691798938</v>
       </c>
     </row>
     <row r="43" spans="1:17">
@@ -2665,13 +2665,13 @@
         <v>-0.1523883420589938</v>
       </c>
       <c r="E43">
-        <v>0.5192370550060136</v>
+        <v>0.3984361203848173</v>
       </c>
       <c r="F43">
-        <v>0.4140242381719635</v>
+        <v>0.2932233035507672</v>
       </c>
       <c r="G43">
-        <v>-0.5664125802309573</v>
+        <v>-0.445611645609761</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -2683,10 +2683,10 @@
         <v>1</v>
       </c>
       <c r="K43">
-        <v>0.3088114213379134</v>
+        <v>0.1880104867167171</v>
       </c>
       <c r="L43">
-        <v>-0.6716253970650075</v>
+        <v>-0.5508244624438111</v>
       </c>
       <c r="M43">
         <v>0.89478718316595</v>
@@ -2698,10 +2698,10 @@
         <v>0.89478718316595</v>
       </c>
       <c r="P43">
-        <v>0.2616358961129697</v>
+        <v>0.1408349614917734</v>
       </c>
       <c r="Q43">
-        <v>0.1481938629983858</v>
+        <v>0.06275769894973646</v>
       </c>
     </row>
     <row r="44" spans="1:17">
@@ -2718,13 +2718,13 @@
         <v>0.4148795034612291</v>
       </c>
       <c r="E44">
-        <v>0.5206063595951018</v>
+        <v>0.4733275747052469</v>
       </c>
       <c r="F44">
-        <v>0.7212560825073833</v>
+        <v>0.6739772976175282</v>
       </c>
       <c r="G44">
-        <v>-0.3063765790461541</v>
+        <v>-0.2590977941562992</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -2736,10 +2736,10 @@
         <v>1</v>
       </c>
       <c r="K44">
-        <v>0.9219058054196647</v>
+        <v>0.8746270205298097</v>
       </c>
       <c r="L44">
-        <v>-0.1057268561338727</v>
+        <v>-0.0584480712440178</v>
       </c>
       <c r="M44">
         <v>1.200649722912281</v>
@@ -2751,10 +2751,10 @@
         <v>1.200649722912281</v>
       </c>
       <c r="P44">
-        <v>0.3063765790461542</v>
+        <v>0.2590977941562991</v>
       </c>
       <c r="Q44">
-        <v>0.3480853341616613</v>
+        <v>0.2821203953115902</v>
       </c>
     </row>
     <row r="45" spans="1:17">
@@ -2771,13 +2771,13 @@
         <v>-0.1722430723603913</v>
       </c>
       <c r="E45">
-        <v>0.531764550366899</v>
+        <v>0.4738675049177161</v>
       </c>
       <c r="F45">
-        <v>0.1200843205918942</v>
+        <v>0.06218727514271133</v>
       </c>
       <c r="G45">
-        <v>-0.2923273929522855</v>
+        <v>-0.2344303475031026</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="K45">
-        <v>-0.2915959091831106</v>
+        <v>-0.3494929546322935</v>
       </c>
       <c r="L45">
-        <v>-0.7040076227272902</v>
+        <v>-0.6461105772781074</v>
       </c>
       <c r="M45">
         <v>0.5883197702249952</v>
@@ -2804,10 +2804,10 @@
         <v>-0.4116802297750048</v>
       </c>
       <c r="P45">
-        <v>-0.05215875176849713</v>
+        <v>-0.11005579721768</v>
       </c>
       <c r="Q45">
-        <v>-0.01524743192413018</v>
+        <v>-0.02580041878647171</v>
       </c>
     </row>
     <row r="46" spans="1:17">
@@ -2824,13 +2824,13 @@
         <v>0.32386998960715</v>
       </c>
       <c r="E46">
-        <v>0.4771990295558996</v>
+        <v>0.3519456421565676</v>
       </c>
       <c r="F46">
-        <v>0.7538901849800064</v>
+        <v>0.6286367975806744</v>
       </c>
       <c r="G46">
-        <v>-0.4300201953728564</v>
+        <v>-0.3047668079735243</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -2842,10 +2842,10 @@
         <v>1</v>
       </c>
       <c r="K46">
-        <v>1.030581340404113</v>
+        <v>0.9053279530047811</v>
       </c>
       <c r="L46">
-        <v>-0.1533290399487496</v>
+        <v>-0.02807565254941763</v>
       </c>
       <c r="M46">
         <v>1.276691155424107</v>
@@ -2857,10 +2857,10 @@
         <v>1.276691155424107</v>
       </c>
       <c r="P46">
-        <v>0.4300201953728564</v>
+        <v>0.3047668079735244</v>
       </c>
       <c r="Q46">
-        <v>0.4634586408410528</v>
+        <v>0.2902924531043503</v>
       </c>
     </row>
     <row r="47" spans="1:17">
@@ -2877,13 +2877,13 @@
         <v>0.0959495356205764</v>
       </c>
       <c r="E47">
-        <v>0.5174406429343102</v>
+        <v>0.4328090033804217</v>
       </c>
       <c r="F47">
-        <v>0.5174406429343102</v>
+        <v>0.4328090033804217</v>
       </c>
       <c r="G47">
-        <v>-0.4214911073137338</v>
+        <v>-0.3368594677598453</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -2895,10 +2895,10 @@
         <v>1</v>
       </c>
       <c r="K47">
-        <v>0.5174406429343102</v>
+        <v>0.4328090033804217</v>
       </c>
       <c r="L47">
-        <v>-0.4214911073137338</v>
+        <v>-0.3368594677598453</v>
       </c>
       <c r="M47">
         <v>1</v>
@@ -2910,10 +2910,10 @@
         <v>1</v>
       </c>
       <c r="P47">
-        <v>0.4214911073137338</v>
+        <v>0.3368594677598453</v>
       </c>
       <c r="Q47">
-        <v>0.2585385055744681</v>
+        <v>0.1781173200213496</v>
       </c>
     </row>
   </sheetData>
